--- a/daybook-generated-files/5.xlsx
+++ b/daybook-generated-files/5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\Shared Files\HV\Capital DayBook\2026\01. JAN\XLSX File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{514E2251-0C6D-4B73-92A0-399E3EBBC274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36C26C5-A8FB-4ACF-8AC4-E43B0BE6C85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{33D816F8-DC63-45B4-9070-884494A5C36B}"/>
   </bookViews>
@@ -1028,9 +1028,6 @@
     <t>ALLOCATION : 29314764-***</t>
   </si>
   <si>
-    <t>ALLOCATION : 29319907-***</t>
-  </si>
-  <si>
     <t>081832502443</t>
   </si>
   <si>
@@ -1311,6 +1308,9 @@
   </si>
   <si>
     <t>ALLOCATION : 29367664-***</t>
+  </si>
+  <si>
+    <t>ALLOCATION : CRRM9907-***</t>
   </si>
 </sst>
 </file>
@@ -7069,7 +7069,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>335</v>
+        <v>429</v>
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -7122,25 +7122,25 @@
         <v>15</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E234" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H234" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="I234" s="2" t="s">
         <v>54</v>
@@ -7152,7 +7152,7 @@
         <v>23</v>
       </c>
       <c r="L234" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="235" spans="1:12" ht="267.75" x14ac:dyDescent="0.2">
@@ -7160,16 +7160,16 @@
         <v>15</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>19</v>
@@ -7178,7 +7178,7 @@
         <v>21</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I235" s="2" t="s">
         <v>54</v>
@@ -7190,7 +7190,7 @@
         <v>23</v>
       </c>
       <c r="L235" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="236" spans="1:12" ht="267.75" x14ac:dyDescent="0.2">
@@ -7198,16 +7198,16 @@
         <v>15</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>19</v>
@@ -7216,7 +7216,7 @@
         <v>21</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I236" s="2" t="s">
         <v>54</v>
@@ -7236,16 +7236,16 @@
         <v>15</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>19</v>
@@ -7254,7 +7254,7 @@
         <v>21</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I237" s="2" t="s">
         <v>54</v>
@@ -7274,16 +7274,16 @@
         <v>15</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>19</v>
@@ -7292,7 +7292,7 @@
         <v>21</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I238" s="2" t="s">
         <v>54</v>
@@ -7304,7 +7304,7 @@
         <v>23</v>
       </c>
       <c r="L238" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="239" spans="1:12" ht="267.75" x14ac:dyDescent="0.2">
@@ -7312,16 +7312,16 @@
         <v>15</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>19</v>
@@ -7330,7 +7330,7 @@
         <v>21</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I239" s="2" t="s">
         <v>54</v>
@@ -7342,7 +7342,7 @@
         <v>23</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="240" spans="1:12" ht="267.75" x14ac:dyDescent="0.2">
@@ -7350,16 +7350,16 @@
         <v>15</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>19</v>
@@ -7368,7 +7368,7 @@
         <v>21</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I240" s="2" t="s">
         <v>54</v>
@@ -7380,7 +7380,7 @@
         <v>23</v>
       </c>
       <c r="L240" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="241" spans="1:12" ht="267.75" x14ac:dyDescent="0.2">
@@ -7388,16 +7388,16 @@
         <v>15</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>19</v>
@@ -7406,7 +7406,7 @@
         <v>21</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I241" s="2" t="s">
         <v>54</v>
@@ -7426,16 +7426,16 @@
         <v>15</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>19</v>
@@ -7444,7 +7444,7 @@
         <v>21</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I242" s="2" t="s">
         <v>54</v>
@@ -7456,7 +7456,7 @@
         <v>23</v>
       </c>
       <c r="L242" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.2">
@@ -7467,12 +7467,12 @@
         <v>21</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -7525,7 +7525,7 @@
         <v>31</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>101</v>
@@ -7534,13 +7534,13 @@
         <v>102</v>
       </c>
       <c r="E248" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F248" s="2" t="s">
+      <c r="G248" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="G248" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>21</v>
@@ -7555,7 +7555,7 @@
         <v>23</v>
       </c>
       <c r="L248" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.2">
@@ -7563,7 +7563,7 @@
         <v>29</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>21</v>
@@ -7571,7 +7571,7 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -7621,25 +7621,25 @@
     </row>
     <row r="254" spans="1:12" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B254" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="C254" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E254" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G254" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G254" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>21</v>
@@ -7654,7 +7654,7 @@
         <v>23</v>
       </c>
       <c r="L254" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
@@ -7662,7 +7662,7 @@
         <v>29</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>21</v>
@@ -7670,7 +7670,7 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -7723,22 +7723,22 @@
         <v>31</v>
       </c>
       <c r="B260" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C260" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="C260" s="2" t="s">
+      <c r="D260" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D260" s="2" t="s">
+      <c r="E260" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="E260" s="2" t="s">
+      <c r="F260" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F260" s="2" t="s">
+      <c r="G260" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>21</v>
@@ -7747,13 +7747,13 @@
         <v>46</v>
       </c>
       <c r="J260" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K260" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L260" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="K260" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L260" s="2" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
@@ -7761,7 +7761,7 @@
         <v>29</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>21</v>
@@ -7769,7 +7769,7 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -7822,22 +7822,22 @@
         <v>31</v>
       </c>
       <c r="B266" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="C266" s="2" t="s">
+      <c r="D266" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D266" s="2" t="s">
+      <c r="E266" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="E266" s="2" t="s">
+      <c r="F266" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F266" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="G266" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>21</v>
@@ -7846,13 +7846,13 @@
         <v>46</v>
       </c>
       <c r="J266" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K266" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L266" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="K266" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L266" s="2" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.2">
@@ -7860,7 +7860,7 @@
         <v>29</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>21</v>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -7921,37 +7921,37 @@
         <v>15</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E272" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G272" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="F272" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G272" s="2" t="s">
+      <c r="H272" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I272" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="H272" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I272" s="2" t="s">
+      <c r="J272" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K272" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="J272" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K272" s="2" t="s">
+      <c r="L272" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="L272" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.2">
@@ -7959,7 +7959,7 @@
         <v>29</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>21</v>
@@ -7967,7 +7967,7 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -8020,37 +8020,37 @@
         <v>15</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I278" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J278" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K278" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="J278" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K278" s="2" t="s">
+      <c r="L278" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="L278" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.2">
@@ -8058,7 +8058,7 @@
         <v>29</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>21</v>
@@ -8066,7 +8066,7 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -8119,37 +8119,37 @@
         <v>15</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I284" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J284" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K284" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="J284" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K284" s="2" t="s">
+      <c r="L284" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="L284" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.2">
@@ -8157,7 +8157,7 @@
         <v>29</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>21</v>
@@ -8165,7 +8165,7 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A288" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -8218,22 +8218,22 @@
         <v>31</v>
       </c>
       <c r="B290" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C290" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E290" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="F290" s="2" t="s">
+      <c r="G290" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="G290" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>21</v>
@@ -8242,13 +8242,13 @@
         <v>54</v>
       </c>
       <c r="J290" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="K290" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L290" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="K290" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L290" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.2">
@@ -8256,7 +8256,7 @@
         <v>29</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>21</v>
@@ -8264,7 +8264,7 @@
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A294" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -8317,22 +8317,22 @@
         <v>31</v>
       </c>
       <c r="B296" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E296" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F296" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="F296" s="2" t="s">
-        <v>396</v>
-      </c>
       <c r="G296" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>21</v>
@@ -8341,13 +8341,13 @@
         <v>54</v>
       </c>
       <c r="J296" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="K296" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L296" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="K296" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L296" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.2">
@@ -8355,7 +8355,7 @@
         <v>29</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>21</v>
@@ -8363,7 +8363,7 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A300" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -8416,22 +8416,22 @@
         <v>31</v>
       </c>
       <c r="B302" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C302" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E302" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F302" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="F302" s="2" t="s">
-        <v>396</v>
-      </c>
       <c r="G302" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>21</v>
@@ -8440,13 +8440,13 @@
         <v>54</v>
       </c>
       <c r="J302" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="K302" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L302" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="K302" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L302" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.2">
@@ -8454,7 +8454,7 @@
         <v>29</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>21</v>
@@ -8462,7 +8462,7 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -8515,22 +8515,22 @@
         <v>31</v>
       </c>
       <c r="B308" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C308" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E308" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F308" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F308" s="2" t="s">
+      <c r="G308" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="G308" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>21</v>
@@ -8539,13 +8539,13 @@
         <v>81</v>
       </c>
       <c r="J308" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="K308" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L308" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="K308" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L308" s="2" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="309" spans="1:12" ht="89.25" x14ac:dyDescent="0.2">
@@ -8553,22 +8553,22 @@
         <v>58</v>
       </c>
       <c r="B309" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C309" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>135</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>21</v>
@@ -8577,13 +8577,13 @@
         <v>97</v>
       </c>
       <c r="J309" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K309" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L309" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="K309" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L309" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="310" spans="1:12" ht="102" x14ac:dyDescent="0.2">
@@ -8591,22 +8591,22 @@
         <v>58</v>
       </c>
       <c r="B310" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C310" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>135</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>21</v>
@@ -8615,13 +8615,13 @@
         <v>97</v>
       </c>
       <c r="J310" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K310" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L310" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.2">
@@ -8629,7 +8629,7 @@
         <v>29</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>21</v>
@@ -8637,7 +8637,7 @@
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -8690,22 +8690,22 @@
         <v>58</v>
       </c>
       <c r="B316" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C316" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>135</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>21</v>
@@ -8714,13 +8714,13 @@
         <v>97</v>
       </c>
       <c r="J316" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K316" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L316" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="K316" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L316" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="317" spans="1:12" ht="102" x14ac:dyDescent="0.2">
@@ -8728,22 +8728,22 @@
         <v>58</v>
       </c>
       <c r="B317" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C317" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>135</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>21</v>
@@ -8752,13 +8752,13 @@
         <v>97</v>
       </c>
       <c r="J317" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K317" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L317" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.2">
@@ -8766,7 +8766,7 @@
         <v>29</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>21</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A321" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -8827,22 +8827,22 @@
         <v>58</v>
       </c>
       <c r="B323" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C323" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="C323" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>135</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>21</v>
@@ -8851,13 +8851,13 @@
         <v>97</v>
       </c>
       <c r="J323" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K323" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L323" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="K323" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L323" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="324" spans="1:12" ht="102" x14ac:dyDescent="0.2">
@@ -8865,22 +8865,22 @@
         <v>58</v>
       </c>
       <c r="B324" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C324" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C324" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>135</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>21</v>
@@ -8889,13 +8889,13 @@
         <v>97</v>
       </c>
       <c r="J324" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K324" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L324" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.2">
@@ -8903,7 +8903,7 @@
         <v>29</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>21</v>
@@ -8911,6 +8911,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A159:H159"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A100:H100"/>
+    <mergeCell ref="A114:H114"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A252:H252"/>
+    <mergeCell ref="A258:H258"/>
+    <mergeCell ref="A173:H173"/>
+    <mergeCell ref="A180:H180"/>
+    <mergeCell ref="A190:H190"/>
+    <mergeCell ref="A197:H197"/>
+    <mergeCell ref="A206:H206"/>
+    <mergeCell ref="A212:H212"/>
     <mergeCell ref="A300:H300"/>
     <mergeCell ref="A306:H306"/>
     <mergeCell ref="A314:H314"/>
@@ -8927,32 +8953,6 @@
     <mergeCell ref="A226:H226"/>
     <mergeCell ref="A232:H232"/>
     <mergeCell ref="A246:H246"/>
-    <mergeCell ref="A252:H252"/>
-    <mergeCell ref="A258:H258"/>
-    <mergeCell ref="A173:H173"/>
-    <mergeCell ref="A180:H180"/>
-    <mergeCell ref="A190:H190"/>
-    <mergeCell ref="A197:H197"/>
-    <mergeCell ref="A206:H206"/>
-    <mergeCell ref="A212:H212"/>
-    <mergeCell ref="A114:H114"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A132:H132"/>
-    <mergeCell ref="A143:H143"/>
-    <mergeCell ref="A150:H150"/>
-    <mergeCell ref="A159:H159"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A100:H100"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="0"/>
